--- a/InputData/fuels/GbPbT/GWP by Pollutant by Timeframe.xlsx
+++ b/InputData/fuels/GbPbT/GWP by Pollutant by Timeframe.xlsx
@@ -1,41 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\fuels\GbPbT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\fuels\GbPbT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2507C16-8FFD-4A24-9319-9C8A1575EA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29895" yWindow="4140" windowWidth="26325" windowHeight="17235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="135" windowWidth="24915" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="GbPbT" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>Source:</t>
   </si>
@@ -118,12 +104,24 @@
     <t>Note</t>
   </si>
   <si>
+    <t>GWP values for VOC, CO, and NOx vary by region.  These values should</t>
+  </si>
+  <si>
+    <t>if creating a version of the model for another country.</t>
+  </si>
+  <si>
+    <t>be updated (likely from the same IPCC source, using different rows in the table)</t>
+  </si>
+  <si>
     <t>p. 740, Table 8.A.6, Row 2 (BC four regions)</t>
   </si>
   <si>
     <t>p. 740, Table 8.A.6, Row 7 (OC four regions)</t>
   </si>
   <si>
+    <t>BC and OC values only include aerosol-radiation interaction.</t>
+  </si>
+  <si>
     <t>100-Year GWP</t>
   </si>
   <si>
@@ -149,15 +147,12 @@
   </si>
   <si>
     <t>Global Warming Potential (g CO2e/g pollutant)</t>
-  </si>
-  <si>
-    <t>We use GWPs for the Kyoto gases (CO2, CH4, N2O, and F-gases)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -250,9 +245,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -290,9 +285,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -327,7 +322,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -362,7 +357,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -535,20 +530,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.1328125" customWidth="1"/>
+    <col min="3" max="3" width="41.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,39 +551,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -596,27 +606,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="18.5703125" customWidth="1"/>
+    <col min="2" max="3" width="18.59765625" customWidth="1"/>
     <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -630,7 +640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -644,7 +654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -658,7 +668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -672,7 +682,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -683,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -697,10 +707,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -711,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -725,10 +735,10 @@
         <v>345</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -739,10 +749,10 @@
         <v>-46</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -756,7 +766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -770,7 +780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -784,12 +794,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="D15" t="s">
         <v>20</v>
       </c>
@@ -800,30 +810,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="17.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="C1" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="str">
         <f>Data!A2</f>
         <v>CO2</v>
@@ -837,103 +847,119 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="str">
         <f>Data!A3</f>
         <v>VOC</v>
       </c>
       <c r="B3" s="4">
-        <v>0</v>
+        <f>Data!B3</f>
+        <v>16.2</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C3</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="str">
         <f>Data!A4</f>
         <v>CO</v>
       </c>
       <c r="B4" s="4">
-        <v>0</v>
+        <f>Data!B4</f>
+        <v>5.6</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C4</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="str">
         <f>Data!A5</f>
         <v>NOx</v>
       </c>
       <c r="B5" s="4">
-        <v>0</v>
+        <f>Data!B5</f>
+        <v>-2.4</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C5</f>
+        <v>-8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="str">
         <f>Data!A6</f>
         <v>PM10</v>
       </c>
       <c r="B6" s="4">
+        <f>Data!B6</f>
         <v>0</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="str">
         <f>Data!A7</f>
         <v>PM25</v>
       </c>
       <c r="B7" s="4">
+        <f>Data!B7</f>
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="str">
         <f>Data!A8</f>
         <v>SOx</v>
       </c>
       <c r="B8" s="4">
+        <f>Data!B8</f>
         <v>0</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="str">
         <f>Data!A9</f>
         <v>BC</v>
       </c>
       <c r="B9" s="4">
-        <v>0</v>
+        <f>Data!B9</f>
+        <v>1200</v>
       </c>
       <c r="C9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C9</f>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="str">
         <f>Data!A10</f>
         <v>OC</v>
       </c>
       <c r="B10" s="4">
-        <v>0</v>
+        <f>Data!B10</f>
+        <v>-160</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <f>Data!C10</f>
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="str">
         <f>Data!A11</f>
         <v>CH4</v>
@@ -947,7 +973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="str">
         <f>Data!A12</f>
         <v>N2O</v>
@@ -961,7 +987,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="str">
         <f>Data!A13</f>
         <v>F gases</v>
@@ -978,4 +1004,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D0C2859-B354-4625-A4A0-AAE722AD08A8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6859AAB8-EE29-42F3-8A89-CDB9179F66B0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19151EF2-6E19-4022-A75B-AAED12801C90}"/>
 </file>